--- a/Value/Value_MATERIAL_PRICES_BEFORE_FINAL_FIXED_V7_CLEAN.xlsx
+++ b/Value/Value_MATERIAL_PRICES_BEFORE_FINAL_FIXED_V7_CLEAN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MauriceSweeney(Brusn\StokPriseUpdate\StokPriseUpdate\Value\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA3C66E-F5E3-4A12-AF22-F7DA2B30909B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1655804-2B1B-4B7E-8853-D2C5891EAA37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="75">
   <si>
     <t>Item Code</t>
   </si>
@@ -111,6 +111,12 @@
     <t>100x1200x12000mm Easy Light 44 (14.4m2) 24/p</t>
   </si>
   <si>
+    <t>ROLL</t>
+  </si>
+  <si>
+    <t>Invoice_312384</t>
+  </si>
+  <si>
     <t>VOL/L44-150</t>
   </si>
   <si>
@@ -123,6 +129,42 @@
     <t>200x1200x6000m Easy Light 44 (7.2m2) 24/p</t>
   </si>
   <si>
+    <t>U/KNA/G/LR44-100</t>
+  </si>
+  <si>
+    <t>Loft Roll 44 CombiCut 100mmx1140x1218 13.89m2</t>
+  </si>
+  <si>
+    <t>9a56b318-cdc5-4bdb-914f-0a6befe846e5</t>
+  </si>
+  <si>
+    <t>U/KNA/G/LR44-150</t>
+  </si>
+  <si>
+    <t>Loft Roll 44Combi Cut 150mm x1140x8050 9.18m2</t>
+  </si>
+  <si>
+    <t>U/KNA/G/LR44-200</t>
+  </si>
+  <si>
+    <t>Loft Roll(Combi Cut) 200mmx1140x6000 (6.84m2)</t>
+  </si>
+  <si>
+    <t>Invoice_306557</t>
+  </si>
+  <si>
+    <t>RAV/120KG-120</t>
+  </si>
+  <si>
+    <t>120x600x1200mm EWI (2/pack) 120kg Pack</t>
+  </si>
+  <si>
+    <t>EACH</t>
+  </si>
+  <si>
+    <t>Invoice_304843 (1)</t>
+  </si>
+  <si>
     <t>Item Type</t>
   </si>
   <si>
@@ -202,6 +244,9 @@
   </si>
   <si>
     <t>22/09/2026</t>
+  </si>
+  <si>
+    <t>Invoice_308294</t>
   </si>
   <si>
     <t>Reason</t>
@@ -613,22 +658,22 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -651,7 +696,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -717,7 +762,7 @@
         <v>14</v>
       </c>
       <c r="J2" s="5">
-        <v>46287.384036773627</v>
+        <v>46287.384328912027</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -740,7 +785,7 @@
         <v>18</v>
       </c>
       <c r="J3" s="5">
-        <v>46287.384037422773</v>
+        <v>46287.388052257527</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -757,22 +802,210 @@
         <v>13</v>
       </c>
       <c r="E4">
+        <v>30</v>
+      </c>
+      <c r="F4">
         <v>2</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
       <c r="G4">
-        <v>18.55</v>
+        <v>17.55</v>
       </c>
       <c r="H4" s="6">
-        <v>18.55</v>
+        <v>8.7750000000000004</v>
       </c>
       <c r="I4" t="s">
         <v>22</v>
       </c>
       <c r="J4" s="5">
-        <v>46287.384037032767</v>
+        <v>46287.384329201392</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5">
+        <v>34.229999999999997</v>
+      </c>
+      <c r="I5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="5">
+        <v>46287.38805262572</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6">
+        <v>34.24</v>
+      </c>
+      <c r="F6">
+        <v>36.97</v>
+      </c>
+      <c r="G6">
+        <v>-2.73</v>
+      </c>
+      <c r="H6" s="6">
+        <v>-7.3843657019204756E-2</v>
+      </c>
+      <c r="I6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="5">
+        <v>46287.388052625982</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7">
+        <v>34.24</v>
+      </c>
+      <c r="F7">
+        <v>36.97</v>
+      </c>
+      <c r="G7">
+        <v>-2.73</v>
+      </c>
+      <c r="H7" s="6">
+        <v>-7.3843657019204756E-2</v>
+      </c>
+      <c r="I7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="5">
+        <v>46287.388052626098</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8">
+        <v>33.06</v>
+      </c>
+      <c r="I8" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" s="5">
+        <v>46287.388050892849</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9">
+        <v>32.78</v>
+      </c>
+      <c r="I9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="5">
+        <v>46287.388050893373</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10">
+        <v>34.24</v>
+      </c>
+      <c r="F10">
+        <v>32.56</v>
+      </c>
+      <c r="G10">
+        <v>1.68</v>
+      </c>
+      <c r="H10" s="6">
+        <v>5.1597051597051587E-2</v>
+      </c>
+      <c r="I10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J10" s="5">
+        <v>46287.388051481357</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11">
+        <v>30</v>
+      </c>
+      <c r="I11" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" s="5">
+        <v>46287.388051184549</v>
       </c>
     </row>
   </sheetData>
@@ -808,46 +1041,46 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -875,10 +1108,10 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -887,31 +1120,31 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -922,7 +1155,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -937,10 +1170,10 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -952,18 +1185,18 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -983,7 +1216,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -1003,7 +1236,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -1023,7 +1256,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -1043,16 +1276,16 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F6">
         <v>34.24</v>
@@ -1063,16 +1296,16 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F7">
         <v>34.24</v>
@@ -1083,7 +1316,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -1106,7 +1339,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -1126,16 +1359,16 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F10">
         <v>34.24</v>
@@ -1146,21 +1379,437 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
       </c>
       <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11">
+        <v>34.24</v>
+      </c>
+      <c r="G11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>19.55</v>
+      </c>
+      <c r="G12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13">
+        <v>34.229999999999997</v>
+      </c>
+      <c r="G13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
         <v>27</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D14" t="s">
         <v>28</v>
       </c>
-      <c r="F11">
-        <v>34.24</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="F14">
+        <v>34.24</v>
+      </c>
+      <c r="G14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15">
+        <v>34.24</v>
+      </c>
+      <c r="G15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16">
+        <v>33.06</v>
+      </c>
+      <c r="G16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17">
+        <v>32.78</v>
+      </c>
+      <c r="G17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18">
+        <v>32.56</v>
+      </c>
+      <c r="G18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19">
+        <v>40.33</v>
+      </c>
+      <c r="G19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20">
+        <v>32.56</v>
+      </c>
+      <c r="F20">
+        <v>34.24</v>
+      </c>
+      <c r="G20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21">
+        <v>34.24</v>
+      </c>
+      <c r="F21">
+        <v>36.97</v>
+      </c>
+      <c r="G21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22">
+        <v>34.24</v>
+      </c>
+      <c r="F22">
+        <v>36.97</v>
+      </c>
+      <c r="G22" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23">
+        <v>36.97</v>
+      </c>
+      <c r="F23">
+        <v>34.24</v>
+      </c>
+      <c r="G23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24">
+        <v>36.97</v>
+      </c>
+      <c r="F24">
+        <v>34.24</v>
+      </c>
+      <c r="G24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25">
+        <v>34.24</v>
+      </c>
+      <c r="F25">
+        <v>32.56</v>
+      </c>
+      <c r="G25" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26">
+        <v>32.56</v>
+      </c>
+      <c r="F26">
+        <v>34.24</v>
+      </c>
+      <c r="G26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27">
+        <v>34.24</v>
+      </c>
+      <c r="F27">
+        <v>36.97</v>
+      </c>
+      <c r="G27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28">
+        <v>34.24</v>
+      </c>
+      <c r="F28">
+        <v>36.97</v>
+      </c>
+      <c r="G28" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29">
+        <v>36.97</v>
+      </c>
+      <c r="F29">
+        <v>34.24</v>
+      </c>
+      <c r="G29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30">
+        <v>36.97</v>
+      </c>
+      <c r="F30">
+        <v>34.24</v>
+      </c>
+      <c r="G30" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1186,7 +1835,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -1195,16 +1844,16 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1224,18 +1873,18 @@
   <sheetData>
     <row r="1" spans="1:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B1" s="2"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
